--- a/Sanjay/Workplan - TSU Analytics - Jun'26.xlsx
+++ b/Sanjay/Workplan - TSU Analytics - Jun'26.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://indeloitte-my.sharepoint.com/personal/sanjgiri_deloitte_com/Documents/Documents/Analytics/Project Mgmt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="216" documentId="8_{727C7EDB-32C3-FA47-9DCE-BCE80E04B4E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B42082E-F517-4B6A-B396-9ADABF9618FA}"/>
+  <xr:revisionPtr revIDLastSave="318" documentId="8_{727C7EDB-32C3-FA47-9DCE-BCE80E04B4E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3DD3A88-2142-4F08-944A-3C414D45631A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{B961CC03-479B-4602-A87D-9B5B11003F64}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="137">
   <si>
     <t>S. No</t>
   </si>
@@ -224,9 +224,6 @@
   </si>
   <si>
     <t>Analysis of Road Cutting Data</t>
-  </si>
-  <si>
-    <t>- Analysis of GST liability though road cutting cotract or permit fee</t>
   </si>
   <si>
     <t>Misclassification of product</t>
@@ -428,10 +425,38 @@
     <t>GST 2.0 Impact analysis</t>
   </si>
   <si>
-    <t>Blocked</t>
-  </si>
-  <si>
-    <t>API not provided by Transport</t>
+    <t xml:space="preserve">GSTR1 HSN Summary Mismatch Correction (FY25-26): Jitu </t>
+  </si>
+  <si>
+    <t>Raise ticket to IT cell (Rajesh L) for Whitelisting of SAS Server (db ctd_gst, user: GST_READ)</t>
+  </si>
+  <si>
+    <t>Jitendra</t>
+  </si>
+  <si>
+    <t>Jitendra, upload in GDRIVE (RJ CTD)</t>
+  </si>
+  <si>
+    <t>Analysis of Workorder report from JDA</t>
+  </si>
+  <si>
+    <t>Meeting date has been postponed</t>
+  </si>
+  <si>
+    <t>- Analysis of GST liability though road cutting contract or permit fee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IFMS Integration </t>
+  </si>
+  <si>
+    <t>API not provided by Transport, 
+Sample data for 1 month of 1 RTO provided on 19 June, without PAN no.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blocked </t>
+  </si>
+  <si>
+    <t>IFMS has not yet shared the API's.</t>
   </si>
 </sst>
 </file>
@@ -455,12 +480,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="5">
@@ -527,7 +558,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -566,8 +597,11 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -590,41 +624,117 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="19">
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C5700"/>
@@ -687,6 +797,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -697,11 +817,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <color rgb="FF9C5700"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1045,52 +1165,52 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8707D53F-5645-43CF-BF53-C28C9147D36A}">
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.7265625" style="10"/>
     <col min="2" max="2" width="25" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="54.90625" style="10" customWidth="1"/>
-    <col min="4" max="4" width="12.54296875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="12.36328125" style="24" customWidth="1"/>
     <col min="5" max="5" width="22.7265625" customWidth="1"/>
-    <col min="6" max="6" width="29.6328125" customWidth="1"/>
+    <col min="6" max="6" width="47.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:6" s="27" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="23" t="s">
-        <v>111</v>
-      </c>
-      <c r="F1" s="23" t="s">
-        <v>113</v>
+      <c r="E1" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="14">
+      <c r="D2" s="23">
         <v>46183</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -1098,15 +1218,17 @@
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="28"/>
+      <c r="B3" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="C3" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="14">
+      <c r="D3" s="23">
         <v>46183</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F3" s="2"/>
     </row>
@@ -1115,680 +1237,754 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D4" s="14">
+      <c r="D4" s="23">
         <v>46184</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="23">
         <v>46185</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F5" s="24" t="s">
-        <v>115</v>
+        <v>111</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="27"/>
+      <c r="B6" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="C6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="23">
         <v>46185</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>115</v>
+        <v>111</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="27"/>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="C7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="23">
         <v>46185</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F7" s="24" t="s">
-        <v>115</v>
+        <v>111</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="27"/>
+      <c r="B8" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="C8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="23">
         <v>46185</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F8" s="24" t="s">
-        <v>115</v>
+        <v>111</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="28"/>
+      <c r="B9" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="C9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="23">
         <v>46185</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F9" s="24" t="s">
-        <v>115</v>
+        <v>111</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="23">
         <v>46185</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F10" s="24" t="s">
-        <v>115</v>
+        <v>111</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="30"/>
+      <c r="B11" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="C11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="23">
         <v>46185</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F11" s="24" t="s">
-        <v>115</v>
+        <v>111</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="30"/>
+      <c r="B12" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="C12" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="23">
         <v>46185</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F12" s="24" t="s">
-        <v>115</v>
+        <v>111</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="30"/>
+      <c r="B13" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="C13" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="23">
         <v>46185</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F13" s="24" t="s">
-        <v>115</v>
+        <v>111</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="30"/>
+      <c r="B14" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="C14" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="23">
         <v>46185</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F14" s="24" t="s">
-        <v>115</v>
+        <v>111</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" s="30"/>
+      <c r="B15" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="C15" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="23">
         <v>46185</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F15" s="24" t="s">
-        <v>115</v>
+        <v>111</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="31"/>
+      <c r="B16" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="C16" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="23">
         <v>46185</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F16" s="24" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+        <v>111</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="B17" s="29" t="s">
-        <v>118</v>
+      <c r="B17" s="4" t="s">
+        <v>117</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D17" s="14">
+        <v>116</v>
+      </c>
+      <c r="D17" s="23">
         <v>46185</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F17" s="24" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+        <v>111</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="B18" s="30"/>
+      <c r="B18" s="4" t="s">
+        <v>117</v>
+      </c>
       <c r="C18" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D18" s="14">
-        <v>46189</v>
+      <c r="D18" s="23">
+        <v>46188</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F18" s="24" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="F18" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="B19" s="30"/>
+      <c r="B19" s="4" t="s">
+        <v>65</v>
+      </c>
       <c r="C19" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D19" s="14">
+        <v>32</v>
+      </c>
+      <c r="D19" s="23">
         <v>46188</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="F19" s="24"/>
-    </row>
-    <row r="20" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+      <c r="F19" s="2"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
-        <v>17</v>
-      </c>
-      <c r="B20" s="30"/>
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>117</v>
+      </c>
       <c r="C20" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D20" s="14">
+        <v>122</v>
+      </c>
+      <c r="D20" s="23">
         <v>46189</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F20" s="24" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+        <v>111</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
-        <v>18</v>
-      </c>
-      <c r="B21" s="31"/>
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>117</v>
+      </c>
       <c r="C21" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D21" s="14">
+        <v>118</v>
+      </c>
+      <c r="D21" s="23">
         <v>46189</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F21" s="24" t="s">
-        <v>121</v>
+        <v>111</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
-        <v>19</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>60</v>
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>117</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D22" s="14">
-        <v>46193</v>
+        <v>119</v>
+      </c>
+      <c r="D22" s="23">
+        <v>46189</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="F22" s="24" t="s">
-        <v>122</v>
+        <v>111</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
-        <v>20</v>
-      </c>
-      <c r="B23" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D23" s="14">
+      <c r="D23" s="23">
         <v>46190</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="F23" s="2"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
-        <v>21</v>
-      </c>
-      <c r="B24" s="27"/>
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="C24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D24" s="14">
+      <c r="D24" s="23">
         <v>46190</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="F24" s="2"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
-        <v>22</v>
-      </c>
-      <c r="B25" s="27"/>
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="C25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D25" s="14">
+      <c r="D25" s="23">
         <v>46190</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="F25" s="2"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
-        <v>23</v>
-      </c>
-      <c r="B26" s="27"/>
+        <v>25</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="C26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D26" s="14">
+      <c r="D26" s="23">
         <v>46190</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="F26" s="2"/>
     </row>
     <row r="27" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
-        <v>24</v>
-      </c>
-      <c r="B27" s="27"/>
+        <v>26</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="C27" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="23">
         <v>46190</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="F27" s="2"/>
     </row>
     <row r="28" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
-        <v>25</v>
-      </c>
-      <c r="B28" s="28"/>
+        <v>27</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="C28" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D28" s="14">
+      <c r="D28" s="23">
         <v>46190</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="F28" s="2"/>
     </row>
-    <row r="29" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D29" s="23">
+        <v>46191</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F29" s="2"/>
+    </row>
+    <row r="30" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D30" s="23">
+        <v>46198</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F30" s="28" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B29" s="25" t="s">
-        <v>126</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D29" s="13">
-        <v>46191</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F29" s="2"/>
-    </row>
-    <row r="30" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A30" s="1">
+      <c r="D31" s="23">
+        <v>46198</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F31" s="28" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="48.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D30" s="13">
+      <c r="D32" s="23">
         <v>46198</v>
       </c>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-    </row>
-    <row r="31" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="1">
+      <c r="E32" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F32" s="28" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B31" s="26" t="s">
+      <c r="D33" s="23">
+        <v>46198</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F33" s="28" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D31" s="14">
-        <v>46191</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A32" s="1">
+      <c r="C34" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B32" s="27"/>
-      <c r="C32" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D32" s="14">
-        <v>46191</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="1">
+      <c r="D34" s="23">
+        <v>46198</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F34" s="28" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B33" s="27"/>
-      <c r="C33" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D33" s="14">
-        <v>46191</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" s="1">
-        <v>31</v>
-      </c>
-      <c r="B34" s="27"/>
-      <c r="C34" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D34" s="14">
-        <v>46191</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" s="1">
-        <v>32</v>
-      </c>
-      <c r="B35" s="27"/>
-      <c r="C35" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D35" s="14">
-        <v>46191</v>
+      <c r="D35" s="23">
+        <v>46198</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+      <c r="F35" s="28" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
-        <v>33</v>
-      </c>
-      <c r="B36" s="28"/>
+        <v>35</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="C36" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D36" s="14">
-        <v>46191</v>
+        <v>55</v>
+      </c>
+      <c r="D36" s="23">
+        <v>46192</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>53</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D37" s="14">
+        <v>54</v>
+      </c>
+      <c r="D37" s="23">
         <v>46192</v>
       </c>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-    </row>
-    <row r="38" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="E37" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
-        <v>35</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D38" s="14">
+        <v>37</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D38" s="23">
         <v>46192</v>
       </c>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-    </row>
-    <row r="39" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="E38" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D39" s="13">
-        <v>46195</v>
-      </c>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
+        <v>60</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D39" s="23">
+        <v>46193</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="40" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
-        <v>37</v>
-      </c>
-      <c r="B40" s="29" t="s">
-        <v>56</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D40" s="14">
-        <v>46197</v>
-      </c>
-      <c r="E40" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D40" s="23">
+        <v>46195</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>115</v>
+      </c>
       <c r="F40" s="2"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
-        <v>38</v>
-      </c>
-      <c r="B41" s="30"/>
-      <c r="C41" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D41" s="14">
-        <v>46197</v>
-      </c>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="D41" s="23">
+        <v>46195</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="42" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
-        <v>39</v>
-      </c>
-      <c r="B42" s="31"/>
+        <v>41</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>56</v>
+      </c>
       <c r="C42" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D42" s="14">
+        <v>57</v>
+      </c>
+      <c r="D42" s="23">
         <v>46197</v>
       </c>
       <c r="E42" s="2"/>
@@ -1796,275 +1992,395 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
-        <v>40</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>64</v>
+        <v>42</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D43" s="13">
+        <v>58</v>
+      </c>
+      <c r="D43" s="23">
         <v>46197</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
     </row>
-    <row r="44" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
-        <v>41</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>92</v>
+        <v>43</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D44" s="13">
-        <v>46202</v>
+        <v>59</v>
+      </c>
+      <c r="D44" s="23">
+        <v>46197</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
     </row>
-    <row r="45" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D45" s="13">
-        <v>46203</v>
+        <v>63</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D45" s="23">
+        <v>46197</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
     </row>
-    <row r="46" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="D46" s="13">
-        <v>46203</v>
-      </c>
-      <c r="E46" s="2"/>
+        <v>117</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D46" s="23">
+        <v>46198</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>115</v>
+      </c>
       <c r="F46" s="2"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D47" s="13">
-        <v>46218</v>
+        <v>61</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D47" s="23">
+        <v>46198</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
     </row>
-    <row r="48" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
-        <v>45</v>
-      </c>
-      <c r="B48" s="26" t="s">
-        <v>31</v>
+        <v>47</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D48" s="14"/>
+        <v>62</v>
+      </c>
+      <c r="D48" s="23">
+        <v>46202</v>
+      </c>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
     </row>
-    <row r="49" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
-        <v>46</v>
-      </c>
-      <c r="B49" s="27"/>
-      <c r="C49" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D49" s="14"/>
+        <v>48</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D49" s="23">
+        <v>46203</v>
+      </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
     </row>
-    <row r="50" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
-        <v>47</v>
-      </c>
-      <c r="B50" s="27"/>
-      <c r="C50" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D50" s="14"/>
+        <v>49</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D50" s="23">
+        <v>46203</v>
+      </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
     </row>
     <row r="51" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
-        <v>48</v>
-      </c>
-      <c r="B51" s="27"/>
-      <c r="C51" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D51" s="14"/>
+        <v>50</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D51" s="23">
+        <v>46218</v>
+      </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
     </row>
     <row r="52" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
-        <v>49</v>
-      </c>
-      <c r="B52" s="27"/>
+        <v>51</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="C52" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D52" s="14"/>
+        <v>32</v>
+      </c>
+      <c r="D52" s="23"/>
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
     </row>
-    <row r="53" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
-        <v>50</v>
-      </c>
-      <c r="B53" s="27"/>
+        <v>52</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="C53" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D53" s="14"/>
+        <v>33</v>
+      </c>
+      <c r="D53" s="23"/>
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
     </row>
     <row r="54" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
-        <v>51</v>
-      </c>
-      <c r="B54" s="28"/>
+        <v>53</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="C54" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D54" s="14"/>
+        <v>44</v>
+      </c>
+      <c r="D54" s="23"/>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
-        <v>52</v>
-      </c>
-      <c r="B55" s="29" t="s">
-        <v>66</v>
+        <v>54</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D55" s="14">
-        <v>46188</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>116</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="D55" s="23"/>
+      <c r="E55" s="2"/>
       <c r="F55" s="2"/>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
-        <v>53</v>
-      </c>
-      <c r="B56" s="30"/>
+        <v>55</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="C56" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D56" s="14"/>
+        <v>35</v>
+      </c>
+      <c r="D56" s="23"/>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
-        <v>54</v>
-      </c>
-      <c r="B57" s="30"/>
+        <v>56</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="C57" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D57" s="14"/>
+        <v>36</v>
+      </c>
+      <c r="D57" s="23"/>
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
-        <v>55</v>
-      </c>
-      <c r="B58" s="30"/>
+        <v>57</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="C58" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D58" s="14"/>
+        <v>37</v>
+      </c>
+      <c r="D58" s="23"/>
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
-        <v>56</v>
-      </c>
-      <c r="B59" s="31"/>
+        <v>58</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>65</v>
+      </c>
       <c r="C59" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D59" s="14"/>
+        <v>66</v>
+      </c>
+      <c r="D59" s="23"/>
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A60" s="22"/>
+      <c r="A60" s="1">
+        <v>59</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D60" s="23"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A61" s="1">
+        <v>60</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D61" s="23"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A62" s="1">
+        <v>61</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D62" s="23"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A63" s="1">
+        <v>62</v>
+      </c>
+      <c r="B63" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D63" s="23"/>
+      <c r="E63" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A64" s="14"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D59">
-    <sortCondition ref="D1:D59"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F64">
+    <sortCondition ref="D1:D64"/>
   </sortState>
-  <mergeCells count="9">
-    <mergeCell ref="B40:B42"/>
-    <mergeCell ref="B48:B54"/>
-    <mergeCell ref="B55:B59"/>
-    <mergeCell ref="B23:B28"/>
-    <mergeCell ref="B17:B21"/>
-    <mergeCell ref="B10:B16"/>
-    <mergeCell ref="B5:B9"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B31:B36"/>
-  </mergeCells>
   <conditionalFormatting sqref="E1:E1048576">
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="14" operator="equal">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E22:E28">
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
+  <conditionalFormatting sqref="E19">
+    <cfRule type="cellIs" dxfId="17" priority="12" operator="equal">
       <formula>"Inprogress"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E19">
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+  <conditionalFormatting sqref="E22:E28">
+    <cfRule type="cellIs" dxfId="16" priority="13" operator="equal">
       <formula>"Inprogress"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E31:E36">
+  <conditionalFormatting sqref="E30:E37">
+    <cfRule type="cellIs" dxfId="15" priority="11" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E58">
+    <cfRule type="cellIs" dxfId="14" priority="10" operator="equal">
+      <formula>"Inprogress"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E30:E35">
+    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
+      <formula>"Inprogress"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E18">
+    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E18">
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+      <formula>"Inprogress"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E39">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E39">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+      <formula>"Inprogress"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E41">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E41">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"Inprogress"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E40">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E55">
+  <conditionalFormatting sqref="E40">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"Inprogress"</formula>
     </cfRule>
@@ -2103,93 +2419,93 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A2" s="15">
+      <c r="A2" s="16">
         <v>1</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" s="18">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="16"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D2" s="17">
-        <v>46192</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="15"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="19"/>
+    </row>
+    <row r="4" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A4" s="16"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D3" s="18"/>
-    </row>
-    <row r="4" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="15"/>
-      <c r="B4" s="16"/>
-      <c r="C4" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D4" s="19"/>
+      <c r="D4" s="20"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="15">
+      <c r="A5" s="16">
         <v>2</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="21" t="s">
         <v>43</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="18">
         <v>46196</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="15"/>
-      <c r="B6" s="20"/>
+      <c r="A6" s="16"/>
+      <c r="B6" s="21"/>
       <c r="C6" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="18"/>
+      <c r="D6" s="19"/>
     </row>
     <row r="7" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A7" s="15"/>
-      <c r="B7" s="20"/>
+      <c r="A7" s="16"/>
+      <c r="B7" s="21"/>
       <c r="C7" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D7" s="18"/>
+      <c r="D7" s="19"/>
     </row>
     <row r="8" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" s="15"/>
-      <c r="B8" s="20"/>
+      <c r="A8" s="16"/>
+      <c r="B8" s="21"/>
       <c r="C8" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="18"/>
+      <c r="D8" s="19"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="15"/>
-      <c r="B9" s="20"/>
+      <c r="A9" s="16"/>
+      <c r="B9" s="21"/>
       <c r="C9" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="19"/>
+      <c r="D9" s="20"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="8">
         <v>3</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C10" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>104</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -2197,11 +2513,11 @@
         <v>4</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C11" s="15"/>
+        <v>94</v>
+      </c>
+      <c r="C11" s="16"/>
       <c r="D11" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -2209,11 +2525,11 @@
         <v>5</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C12" s="15"/>
+        <v>95</v>
+      </c>
+      <c r="C12" s="16"/>
       <c r="D12" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
@@ -2221,11 +2537,11 @@
         <v>6</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C13" s="15"/>
+        <v>96</v>
+      </c>
+      <c r="C13" s="16"/>
       <c r="D13" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
@@ -2233,11 +2549,11 @@
         <v>1</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C14" s="15"/>
+        <v>97</v>
+      </c>
+      <c r="C14" s="16"/>
       <c r="D14" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
@@ -2245,11 +2561,11 @@
         <v>8</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C15" s="15"/>
+        <v>98</v>
+      </c>
+      <c r="C15" s="16"/>
       <c r="D15" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
@@ -2257,11 +2573,11 @@
         <v>9</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C16" s="15"/>
+        <v>99</v>
+      </c>
+      <c r="C16" s="16"/>
       <c r="D16" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -2269,11 +2585,11 @@
         <v>10</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C17" s="15"/>
+        <v>100</v>
+      </c>
+      <c r="C17" s="16"/>
       <c r="D17" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -2281,11 +2597,11 @@
         <v>11</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C18" s="15"/>
+        <v>101</v>
+      </c>
+      <c r="C18" s="16"/>
       <c r="D18" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -2293,11 +2609,11 @@
         <v>12</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C19" s="15"/>
+        <v>102</v>
+      </c>
+      <c r="C19" s="16"/>
       <c r="D19" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -2305,11 +2621,11 @@
         <v>13</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C20" s="15"/>
+        <v>109</v>
+      </c>
+      <c r="C20" s="16"/>
       <c r="D20" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -2356,90 +2672,90 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="15">
+      <c r="A2" s="16">
         <v>1</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="17" t="s">
         <v>42</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="21" t="s">
-        <v>107</v>
+      <c r="D2" s="22" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="15"/>
-      <c r="B3" s="16"/>
+      <c r="A3" s="16"/>
+      <c r="B3" s="17"/>
       <c r="C3" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D3" s="21"/>
+      <c r="D3" s="22"/>
     </row>
     <row r="4" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A4" s="15"/>
-      <c r="B4" s="16"/>
+      <c r="A4" s="16"/>
+      <c r="B4" s="17"/>
       <c r="C4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D4" s="21"/>
+      <c r="D4" s="22"/>
     </row>
     <row r="5" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A5" s="15"/>
-      <c r="B5" s="16"/>
+      <c r="A5" s="16"/>
+      <c r="B5" s="17"/>
       <c r="C5" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="21"/>
+      <c r="D5" s="22"/>
     </row>
     <row r="6" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A6" s="15">
+      <c r="A6" s="16">
         <v>2</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="18">
+        <v>46190</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A7" s="16"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D6" s="17">
-        <v>46190</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A7" s="15"/>
-      <c r="B7" s="20"/>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="19"/>
+    </row>
+    <row r="8" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A8" s="16"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D7" s="18"/>
-    </row>
-    <row r="8" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" s="15"/>
-      <c r="B8" s="20"/>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="19"/>
+    </row>
+    <row r="9" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A9" s="16"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D8" s="18"/>
-    </row>
-    <row r="9" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A9" s="15"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D9" s="19"/>
+      <c r="D9" s="20"/>
     </row>
     <row r="10" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="8">
         <v>3</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="D10" s="13">
         <v>46191</v>
@@ -2450,10 +2766,10 @@
         <v>4</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D11" s="13">
         <v>46194</v>
@@ -2464,13 +2780,13 @@
         <v>5</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>108</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/Sanjay/Workplan - TSU Analytics - Jun'26.xlsx
+++ b/Sanjay/Workplan - TSU Analytics - Jun'26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://indeloitte-my.sharepoint.com/personal/sanjgiri_deloitte_com/Documents/Documents/Analytics/Project Mgmt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="318" documentId="8_{727C7EDB-32C3-FA47-9DCE-BCE80E04B4E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3DD3A88-2142-4F08-944A-3C414D45631A}"/>
+  <xr:revisionPtr revIDLastSave="417" documentId="8_{727C7EDB-32C3-FA47-9DCE-BCE80E04B4E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E37D672-9D44-451B-B1D5-680C85EFCAA5}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{B961CC03-479B-4602-A87D-9B5B11003F64}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="158">
   <si>
     <t>S. No</t>
   </si>
@@ -380,9 +380,6 @@
   </si>
   <si>
     <t>Comment</t>
-  </si>
-  <si>
-    <t>Not enough Potential</t>
   </si>
   <si>
     <t>SHARED</t>
@@ -431,9 +428,6 @@
     <t>Raise ticket to IT cell (Rajesh L) for Whitelisting of SAS Server (db ctd_gst, user: GST_READ)</t>
   </si>
   <si>
-    <t>Jitendra</t>
-  </si>
-  <si>
     <t>Jitendra, upload in GDRIVE (RJ CTD)</t>
   </si>
   <si>
@@ -457,13 +451,83 @@
   </si>
   <si>
     <t>IFMS has not yet shared the API's.</t>
+  </si>
+  <si>
+    <t>SHARED to ACCT_BIU</t>
+  </si>
+  <si>
+    <t>No of taxpayer</t>
+  </si>
+  <si>
+    <t>Potential</t>
+  </si>
+  <si>
+    <t>Uplaoded on Feedback (Yes/No)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incharge </t>
+  </si>
+  <si>
+    <t>Jitendra P</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>Connect with 
+rajesh gadwal ji</t>
+  </si>
+  <si>
+    <t>Sanjay Giri</t>
+  </si>
+  <si>
+    <t>DP, JP</t>
+  </si>
+  <si>
+    <t>DP</t>
+  </si>
+  <si>
+    <t>RK</t>
+  </si>
+  <si>
+    <t>SG</t>
+  </si>
+  <si>
+    <t>AJ</t>
+  </si>
+  <si>
+    <t>Mailed</t>
+  </si>
+  <si>
+    <t>JP</t>
+  </si>
+  <si>
+    <t>LP</t>
+  </si>
+  <si>
+    <t>JP/LP</t>
+  </si>
+  <si>
+    <t>SL/RK</t>
+  </si>
+  <si>
+    <t>YK/DP/AJ</t>
+  </si>
+  <si>
+    <t>YK/AJ</t>
+  </si>
+  <si>
+    <t>MC</t>
+  </si>
+  <si>
+    <t>SG/AJ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -474,6 +538,14 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -494,7 +566,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -554,11 +626,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -603,6 +688,22 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -624,67 +725,18 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="19">
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="9">
     <dxf>
       <font>
         <color rgb="FF9C5700"/>
@@ -747,46 +799,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -802,26 +814,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1165,38 +1157,54 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8707D53F-5645-43CF-BF53-C28C9147D36A}">
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.7265625" style="10"/>
     <col min="2" max="2" width="25" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="54.90625" style="10" customWidth="1"/>
-    <col min="4" max="4" width="12.36328125" style="24" customWidth="1"/>
-    <col min="5" max="5" width="22.7265625" customWidth="1"/>
-    <col min="6" max="6" width="47.36328125" customWidth="1"/>
+    <col min="4" max="4" width="12.36328125" style="17" customWidth="1"/>
+    <col min="5" max="5" width="12.1796875" customWidth="1"/>
+    <col min="6" max="6" width="13.453125" customWidth="1"/>
+    <col min="7" max="7" width="11.1796875" customWidth="1"/>
+    <col min="8" max="8" width="20.453125" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="10.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="27" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:10" s="20" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="F1" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="H1" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="I1" s="18" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="J1" s="29" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1206,15 +1214,23 @@
       <c r="C2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="23">
+      <c r="D2" s="16">
         <v>46183</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>111</v>
       </c>
       <c r="F2" s="2"/>
-    </row>
-    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="G2" s="2"/>
+      <c r="H2" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1224,15 +1240,23 @@
       <c r="C3" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="23">
+      <c r="D3" s="16">
         <v>46183</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>111</v>
       </c>
       <c r="F3" s="2"/>
-    </row>
-    <row r="4" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="G3" s="2"/>
+      <c r="H3" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1242,17 +1266,25 @@
       <c r="C4" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D4" s="23">
+      <c r="D4" s="16">
         <v>46184</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+        <v>114</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I4" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1262,17 +1294,25 @@
       <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="23">
+      <c r="D5" s="16">
         <v>46185</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1282,17 +1322,25 @@
       <c r="C6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="23">
+      <c r="D6" s="16">
         <v>46185</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1302,17 +1350,25 @@
       <c r="C7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="16">
         <v>46185</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1322,17 +1378,25 @@
       <c r="C8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="16">
         <v>46185</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1342,17 +1406,25 @@
       <c r="C9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="23">
+      <c r="D9" s="16">
         <v>46185</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1362,17 +1434,25 @@
       <c r="C10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="16">
         <v>46185</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1382,17 +1462,25 @@
       <c r="C11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="23">
+      <c r="D11" s="16">
         <v>46185</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1402,17 +1490,25 @@
       <c r="C12" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="23">
+      <c r="D12" s="16">
         <v>46185</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1422,17 +1518,25 @@
       <c r="C13" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="23">
+      <c r="D13" s="16">
         <v>46185</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1442,17 +1546,25 @@
       <c r="C14" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="23">
+      <c r="D14" s="16">
         <v>46185</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1462,17 +1574,25 @@
       <c r="C15" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D15" s="23">
+      <c r="D15" s="16">
         <v>46185</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1482,57 +1602,81 @@
       <c r="C16" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="23">
+      <c r="D16" s="16">
         <v>46185</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D17" s="23">
+        <v>115</v>
+      </c>
+      <c r="D17" s="16">
         <v>46185</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D18" s="23">
+        <v>122</v>
+      </c>
+      <c r="D18" s="16">
         <v>46188</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+        <v>114</v>
+      </c>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -1542,75 +1686,107 @@
       <c r="C19" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D19" s="23">
+      <c r="D19" s="16">
         <v>46188</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F19" s="2"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G19" s="2"/>
+      <c r="H19" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D20" s="23">
+        <v>121</v>
+      </c>
+      <c r="D20" s="16">
         <v>46189</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D21" s="23">
+      <c r="D21" s="16">
         <v>46189</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D22" s="23">
+        <v>118</v>
+      </c>
+      <c r="D22" s="16">
         <v>46189</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -1620,15 +1796,23 @@
       <c r="C23" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D23" s="23">
+      <c r="D23" s="16">
         <v>46190</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>111</v>
       </c>
       <c r="F23" s="2"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G23" s="2"/>
+      <c r="H23" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -1638,15 +1822,23 @@
       <c r="C24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D24" s="23">
+      <c r="D24" s="16">
         <v>46190</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>111</v>
       </c>
       <c r="F24" s="2"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G24" s="2"/>
+      <c r="H24" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -1656,15 +1848,23 @@
       <c r="C25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D25" s="23">
+      <c r="D25" s="16">
         <v>46190</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>111</v>
       </c>
       <c r="F25" s="2"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G25" s="2"/>
+      <c r="H25" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -1674,15 +1874,23 @@
       <c r="C26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D26" s="23">
+      <c r="D26" s="16">
         <v>46190</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>111</v>
       </c>
       <c r="F26" s="2"/>
-    </row>
-    <row r="27" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="G26" s="2"/>
+      <c r="H26" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -1692,15 +1900,23 @@
       <c r="C27" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D27" s="23">
+      <c r="D27" s="16">
         <v>46190</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>111</v>
       </c>
       <c r="F27" s="2"/>
-    </row>
-    <row r="28" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="G27" s="2"/>
+      <c r="H27" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -1710,33 +1926,49 @@
       <c r="C28" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D28" s="23">
+      <c r="D28" s="16">
         <v>46190</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>111</v>
       </c>
       <c r="F28" s="2"/>
-    </row>
-    <row r="29" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+      <c r="G28" s="2"/>
+      <c r="H28" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>28</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D29" s="23">
+        <v>123</v>
+      </c>
+      <c r="D29" s="16">
         <v>46191</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>111</v>
       </c>
       <c r="F29" s="2"/>
-    </row>
-    <row r="30" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="G29" s="2"/>
+      <c r="H29" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -1746,17 +1978,25 @@
       <c r="C30" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D30" s="23">
+      <c r="D30" s="16">
         <v>46198</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F30" s="28" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+        <v>114</v>
+      </c>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I30" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -1766,17 +2006,25 @@
       <c r="C31" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D31" s="23">
+      <c r="D31" s="16">
         <v>46198</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F31" s="28" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="48.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>114</v>
+      </c>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I31" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="48.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -1786,17 +2034,25 @@
       <c r="C32" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="23">
+      <c r="D32" s="16">
         <v>46198</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F32" s="28" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+        <v>114</v>
+      </c>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I32" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -1806,17 +2062,25 @@
       <c r="C33" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="23">
+      <c r="D33" s="16">
         <v>46198</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F33" s="28" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+        <v>114</v>
+      </c>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I33" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -1826,17 +2090,25 @@
       <c r="C34" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D34" s="23">
+      <c r="D34" s="16">
         <v>46198</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F34" s="28" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+        <v>114</v>
+      </c>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I34" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -1846,17 +2118,25 @@
       <c r="C35" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="23">
+      <c r="D35" s="16">
         <v>46198</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F35" s="28" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+        <v>114</v>
+      </c>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I35" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -1866,17 +2146,25 @@
       <c r="C36" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D36" s="23">
+      <c r="D36" s="16">
         <v>46192</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F36" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -1886,37 +2174,51 @@
       <c r="C37" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D37" s="23">
+      <c r="D37" s="16">
         <v>46192</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F37" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>37</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="D38" s="23">
+        <v>126</v>
+      </c>
+      <c r="D38" s="16">
         <v>46192</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F38" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -1924,19 +2226,24 @@
         <v>60</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="D39" s="23">
+        <v>130</v>
+      </c>
+      <c r="D39" s="16">
         <v>46193</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+        <v>114</v>
+      </c>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -1946,35 +2253,49 @@
       <c r="C40" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="D40" s="23">
+      <c r="D40" s="16">
         <v>46195</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F40" s="2"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G40" s="2"/>
+      <c r="H40" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>40</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="D41" s="23">
+        <v>128</v>
+      </c>
+      <c r="D41" s="16">
         <v>46195</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+        <v>114</v>
+      </c>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -1984,13 +2305,21 @@
       <c r="C42" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D42" s="23">
+      <c r="D42" s="16">
         <v>46197</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G42" s="2"/>
+      <c r="H42" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -2000,13 +2329,21 @@
       <c r="C43" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D43" s="23">
+      <c r="D43" s="16">
         <v>46197</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
-    </row>
-    <row r="44" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="G43" s="2"/>
+      <c r="H43" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -2016,13 +2353,21 @@
       <c r="C44" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D44" s="23">
+      <c r="D44" s="16">
         <v>46197</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G44" s="2"/>
+      <c r="H44" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -2032,31 +2377,47 @@
       <c r="C45" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D45" s="23">
+      <c r="D45" s="16">
         <v>46197</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G45" s="2"/>
+      <c r="H45" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I45" s="2"/>
+      <c r="J45" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <v>45</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D46" s="23">
+        <v>125</v>
+      </c>
+      <c r="D46" s="16">
         <v>46198</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F46" s="2"/>
-    </row>
-    <row r="47" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="G46" s="2"/>
+      <c r="H46" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -2066,13 +2427,21 @@
       <c r="C47" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D47" s="23">
+      <c r="D47" s="16">
         <v>46198</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
-    </row>
-    <row r="48" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="G47" s="2"/>
+      <c r="H47" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I47" s="2"/>
+      <c r="J47" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -2082,13 +2451,21 @@
       <c r="C48" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D48" s="23">
+      <c r="D48" s="16">
         <v>46202</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
-    </row>
-    <row r="49" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="G48" s="2"/>
+      <c r="H48" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I48" s="2"/>
+      <c r="J48" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -2098,13 +2475,21 @@
       <c r="C49" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D49" s="23">
+      <c r="D49" s="16">
         <v>46203</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
-    </row>
-    <row r="50" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="G49" s="2"/>
+      <c r="H49" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I49" s="2"/>
+      <c r="J49" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -2114,13 +2499,21 @@
       <c r="C50" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D50" s="23">
-        <v>46203</v>
+      <c r="D50" s="16">
+        <v>46218</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
-    </row>
-    <row r="51" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G50" s="2"/>
+      <c r="H50" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I50" s="2"/>
+      <c r="J50" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -2130,13 +2523,21 @@
       <c r="C51" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="D51" s="23">
+      <c r="D51" s="16">
         <v>46218</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
-    </row>
-    <row r="52" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G51" s="2"/>
+      <c r="H51" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I51" s="2"/>
+      <c r="J51" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -2146,11 +2547,19 @@
       <c r="C52" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D52" s="23"/>
+      <c r="D52" s="16"/>
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
-    </row>
-    <row r="53" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G52" s="2"/>
+      <c r="H52" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I52" s="2"/>
+      <c r="J52" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -2160,11 +2569,19 @@
       <c r="C53" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D53" s="23"/>
+      <c r="D53" s="16"/>
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
-    </row>
-    <row r="54" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G53" s="2"/>
+      <c r="H53" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I53" s="2"/>
+      <c r="J53" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -2174,11 +2591,19 @@
       <c r="C54" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D54" s="23"/>
+      <c r="D54" s="16"/>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
-    </row>
-    <row r="55" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G54" s="2"/>
+      <c r="H54" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I54" s="2"/>
+      <c r="J54" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -2188,11 +2613,19 @@
       <c r="C55" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D55" s="23"/>
+      <c r="D55" s="16"/>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
-    </row>
-    <row r="56" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="G55" s="2"/>
+      <c r="H55" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I55" s="2"/>
+      <c r="J55" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -2202,11 +2635,19 @@
       <c r="C56" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D56" s="23"/>
+      <c r="D56" s="16"/>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
-    </row>
-    <row r="57" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G56" s="2"/>
+      <c r="H56" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -2216,11 +2657,19 @@
       <c r="C57" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D57" s="23"/>
+      <c r="D57" s="16"/>
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
-    </row>
-    <row r="58" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="G57" s="2"/>
+      <c r="H57" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I57" s="2"/>
+      <c r="J57" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -2230,11 +2679,19 @@
       <c r="C58" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D58" s="23"/>
+      <c r="D58" s="16"/>
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G58" s="2"/>
+      <c r="H58" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I58" s="2"/>
+      <c r="J58" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -2244,11 +2701,19 @@
       <c r="C59" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D59" s="23"/>
+      <c r="D59" s="16"/>
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G59" s="2"/>
+      <c r="H59" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I59" s="2"/>
+      <c r="J59" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -2258,11 +2723,19 @@
       <c r="C60" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D60" s="23"/>
+      <c r="D60" s="16"/>
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G60" s="2"/>
+      <c r="H60" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I60" s="2"/>
+      <c r="J60" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -2272,11 +2745,19 @@
       <c r="C61" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D61" s="23"/>
+      <c r="D61" s="16"/>
       <c r="E61" s="2"/>
       <c r="F61" s="2"/>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G61" s="2"/>
+      <c r="H61" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I61" s="2"/>
+      <c r="J61" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -2286,102 +2767,97 @@
       <c r="C62" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D62" s="23"/>
+      <c r="D62" s="16"/>
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G62" s="2"/>
+      <c r="H62" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I62" s="2"/>
+      <c r="J62" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
         <v>62</v>
       </c>
       <c r="B63" s="15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C63" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D63" s="16"/>
+      <c r="E63" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="D63" s="23"/>
-      <c r="E63" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64" s="14"/>
+      <c r="I64" s="2"/>
+      <c r="J64" s="2"/>
+    </row>
+    <row r="65" spans="9:10" x14ac:dyDescent="0.35">
+      <c r="I65" s="2"/>
+      <c r="J65" s="2"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F64">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I64">
     <sortCondition ref="D1:D64"/>
   </sortState>
-  <conditionalFormatting sqref="E1:E1048576">
-    <cfRule type="cellIs" dxfId="18" priority="14" operator="equal">
+  <conditionalFormatting sqref="E1:H1048576">
+    <cfRule type="cellIs" dxfId="8" priority="14" operator="equal">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E19">
-    <cfRule type="cellIs" dxfId="17" priority="12" operator="equal">
-      <formula>"Inprogress"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E22:E28">
-    <cfRule type="cellIs" dxfId="16" priority="13" operator="equal">
-      <formula>"Inprogress"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E30:E37">
-    <cfRule type="cellIs" dxfId="15" priority="11" operator="equal">
-      <formula>"Blocked"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E58">
-    <cfRule type="cellIs" dxfId="14" priority="10" operator="equal">
-      <formula>"Inprogress"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E30:E35">
-    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
-      <formula>"Inprogress"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E18">
+  <conditionalFormatting sqref="E18:H18">
     <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E18">
+  <conditionalFormatting sqref="E18:H19">
     <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
       <formula>"Inprogress"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E39">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+  <conditionalFormatting sqref="E22:H28">
+    <cfRule type="cellIs" dxfId="5" priority="13" operator="equal">
+      <formula>"Inprogress"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E30:H35">
+    <cfRule type="cellIs" dxfId="4" priority="9" operator="equal">
+      <formula>"Inprogress"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E30:H37">
+    <cfRule type="cellIs" dxfId="3" priority="11" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E39">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+  <conditionalFormatting sqref="E39:H41">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Inprogress"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E41">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
-      <formula>"Blocked"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E41">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
-      <formula>"Inprogress"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E40">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E40">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+  <conditionalFormatting sqref="E58:H58">
+    <cfRule type="cellIs" dxfId="0" priority="10" operator="equal">
       <formula>"Inprogress"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2419,80 +2895,80 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A2" s="16">
+      <c r="A2" s="22">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="23" t="s">
         <v>68</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D2" s="18">
+      <c r="D2" s="24">
         <v>46192</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="16"/>
-      <c r="B3" s="17"/>
+      <c r="A3" s="22"/>
+      <c r="B3" s="23"/>
       <c r="C3" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D3" s="19"/>
+      <c r="D3" s="25"/>
     </row>
     <row r="4" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A4" s="16"/>
-      <c r="B4" s="17"/>
+      <c r="A4" s="22"/>
+      <c r="B4" s="23"/>
       <c r="C4" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D4" s="20"/>
+      <c r="D4" s="26"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="16">
+      <c r="A5" s="22">
         <v>2</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="27" t="s">
         <v>43</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="24">
         <v>46196</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="16"/>
-      <c r="B6" s="21"/>
+      <c r="A6" s="22"/>
+      <c r="B6" s="27"/>
       <c r="C6" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="19"/>
+      <c r="D6" s="25"/>
     </row>
     <row r="7" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A7" s="16"/>
-      <c r="B7" s="21"/>
+      <c r="A7" s="22"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D7" s="19"/>
+      <c r="D7" s="25"/>
     </row>
     <row r="8" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" s="16"/>
-      <c r="B8" s="21"/>
+      <c r="A8" s="22"/>
+      <c r="B8" s="27"/>
       <c r="C8" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="19"/>
+      <c r="D8" s="25"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="16"/>
-      <c r="B9" s="21"/>
+      <c r="A9" s="22"/>
+      <c r="B9" s="27"/>
       <c r="C9" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="20"/>
+      <c r="D9" s="26"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="8">
@@ -2501,7 +2977,7 @@
       <c r="B10" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="22" t="s">
         <v>103</v>
       </c>
       <c r="D10" s="8" t="s">
@@ -2515,7 +2991,7 @@
       <c r="B11" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="16"/>
+      <c r="C11" s="22"/>
       <c r="D11" s="8" t="s">
         <v>104</v>
       </c>
@@ -2527,7 +3003,7 @@
       <c r="B12" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="C12" s="16"/>
+      <c r="C12" s="22"/>
       <c r="D12" s="8" t="s">
         <v>105</v>
       </c>
@@ -2539,7 +3015,7 @@
       <c r="B13" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="C13" s="16"/>
+      <c r="C13" s="22"/>
       <c r="D13" s="8" t="s">
         <v>105</v>
       </c>
@@ -2551,7 +3027,7 @@
       <c r="B14" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="C14" s="16"/>
+      <c r="C14" s="22"/>
       <c r="D14" s="8" t="s">
         <v>104</v>
       </c>
@@ -2563,7 +3039,7 @@
       <c r="B15" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="C15" s="16"/>
+      <c r="C15" s="22"/>
       <c r="D15" s="8" t="s">
         <v>105</v>
       </c>
@@ -2575,7 +3051,7 @@
       <c r="B16" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="C16" s="16"/>
+      <c r="C16" s="22"/>
       <c r="D16" s="8" t="s">
         <v>105</v>
       </c>
@@ -2587,7 +3063,7 @@
       <c r="B17" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="C17" s="16"/>
+      <c r="C17" s="22"/>
       <c r="D17" s="8" t="s">
         <v>105</v>
       </c>
@@ -2599,7 +3075,7 @@
       <c r="B18" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="C18" s="16"/>
+      <c r="C18" s="22"/>
       <c r="D18" s="8" t="s">
         <v>105</v>
       </c>
@@ -2611,7 +3087,7 @@
       <c r="B19" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="C19" s="16"/>
+      <c r="C19" s="22"/>
       <c r="D19" s="8" t="s">
         <v>105</v>
       </c>
@@ -2623,7 +3099,7 @@
       <c r="B20" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="C20" s="16"/>
+      <c r="C20" s="22"/>
       <c r="D20" s="8" t="s">
         <v>105</v>
       </c>
@@ -2672,80 +3148,80 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="16">
+      <c r="A2" s="22">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="23" t="s">
         <v>42</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="D2" s="28" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="16"/>
-      <c r="B3" s="17"/>
+      <c r="A3" s="22"/>
+      <c r="B3" s="23"/>
       <c r="C3" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D3" s="22"/>
+      <c r="D3" s="28"/>
     </row>
     <row r="4" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A4" s="16"/>
-      <c r="B4" s="17"/>
+      <c r="A4" s="22"/>
+      <c r="B4" s="23"/>
       <c r="C4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D4" s="22"/>
+      <c r="D4" s="28"/>
     </row>
     <row r="5" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A5" s="16"/>
-      <c r="B5" s="17"/>
+      <c r="A5" s="22"/>
+      <c r="B5" s="23"/>
       <c r="C5" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="22"/>
+      <c r="D5" s="28"/>
     </row>
     <row r="6" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A6" s="16">
+      <c r="A6" s="22">
         <v>2</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="27" t="s">
         <v>73</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="24">
         <v>46190</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A7" s="16"/>
-      <c r="B7" s="21"/>
+      <c r="A7" s="22"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D7" s="19"/>
+      <c r="D7" s="25"/>
     </row>
     <row r="8" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" s="16"/>
-      <c r="B8" s="21"/>
+      <c r="A8" s="22"/>
+      <c r="B8" s="27"/>
       <c r="C8" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D8" s="19"/>
+      <c r="D8" s="25"/>
     </row>
     <row r="9" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A9" s="16"/>
-      <c r="B9" s="21"/>
+      <c r="A9" s="22"/>
+      <c r="B9" s="27"/>
       <c r="C9" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D9" s="20"/>
+      <c r="D9" s="26"/>
     </row>
     <row r="10" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="8">
